--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,6 +786,619 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129556174</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100913</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Dyveln, Dyveln, Dls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>347257</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6542720</v>
+      </c>
+      <c r="S3" t="n">
+        <v>8</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129568972</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Dyveln, Härserud, Dls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>347300</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6542773</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska rejäla hackspår i en stående död gran. På fyndplatsen finns rikligt med stående död ved av gran.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129569041</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100913</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Dyveln, Härserud, Dls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>347267</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6542704</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129569006</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Dyveln, Härserud, Dls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>347438</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6542735</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>En lockande spillkråka i en skog med gott om stående död ved och aspar lämpliga för bohål under kommande häckning.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Med gran, tall och inslag av asp, björk och rönn.</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129568991</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58097</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Dyveln, Härserud, Dls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>347354</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6542779</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>129556174</v>
       </c>
       <c r="B3" t="n">
-        <v>100913</v>
+        <v>100916</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>129569041</v>
       </c>
       <c r="B5" t="n">
-        <v>100913</v>
+        <v>100916</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -906,57 +906,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129568972</v>
+        <v>129569041</v>
       </c>
       <c r="B4" t="n">
-        <v>57724</v>
+        <v>100916</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Dyveln, Härserud, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>347300</v>
+        <v>347267</v>
       </c>
       <c r="R4" t="n">
-        <v>6542773</v>
+        <v>6542704</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -991,43 +987,19 @@
           <t>2025-11-06</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska rejäla hackspår i en stående död gran. På fyndplatsen finns rikligt med stående död ved av gran.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1045,53 +1017,57 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129569041</v>
+        <v>129568972</v>
       </c>
       <c r="B5" t="n">
-        <v>100916</v>
+        <v>57724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dyveln, Härserud, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>347267</v>
+        <v>347300</v>
       </c>
       <c r="R5" t="n">
-        <v>6542704</v>
+        <v>6542773</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1126,19 +1102,43 @@
           <t>2025-11-06</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska rejäla hackspår i en stående död gran. På fyndplatsen finns rikligt med stående död ved av gran.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1400,6 +1400,421 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129626512</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100916</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Dyveln, Dls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>347285</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6542754</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129627015</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Dyveln, Dls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>347315</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6542796</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre grova hackspår i stambasen av en död tall.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129626741</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Dyveln, Dls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>347201</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6542792</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på grenar av en tall.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -906,53 +906,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129569041</v>
+        <v>129568972</v>
       </c>
       <c r="B4" t="n">
-        <v>100916</v>
+        <v>57724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Dyveln, Härserud, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>347267</v>
+        <v>347300</v>
       </c>
       <c r="R4" t="n">
-        <v>6542704</v>
+        <v>6542773</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -987,19 +991,43 @@
           <t>2025-11-06</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska rejäla hackspår i en stående död gran. På fyndplatsen finns rikligt med stående död ved av gran.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1017,57 +1045,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129568972</v>
+        <v>129569041</v>
       </c>
       <c r="B5" t="n">
-        <v>57724</v>
+        <v>100916</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dyveln, Härserud, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>347300</v>
+        <v>347267</v>
       </c>
       <c r="R5" t="n">
-        <v>6542773</v>
+        <v>6542704</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1102,43 +1126,19 @@
           <t>2025-11-06</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska rejäla hackspår i en stående död gran. På fyndplatsen finns rikligt med stående död ved av gran.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>129556174</v>
       </c>
       <c r="B3" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,53 +906,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129569041</v>
+        <v>129568972</v>
       </c>
       <c r="B4" t="n">
-        <v>100916</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Dyveln, Härserud, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>347267</v>
+        <v>347300</v>
       </c>
       <c r="R4" t="n">
-        <v>6542704</v>
+        <v>6542773</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -987,19 +991,43 @@
           <t>2025-11-06</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska rejäla hackspår i en stående död gran. På fyndplatsen finns rikligt med stående död ved av gran.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1017,57 +1045,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129568972</v>
+        <v>129569041</v>
       </c>
       <c r="B5" t="n">
-        <v>57724</v>
+        <v>100945</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dyveln, Härserud, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>347300</v>
+        <v>347267</v>
       </c>
       <c r="R5" t="n">
-        <v>6542773</v>
+        <v>6542704</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1102,43 +1126,19 @@
           <t>2025-11-06</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska rejäla hackspår i en stående död gran. På fyndplatsen finns rikligt med stående död ved av gran.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1159,7 +1159,7 @@
         <v>129569006</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>129568991</v>
       </c>
       <c r="B7" t="n">
-        <v>58097</v>
+        <v>58100</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>129626512</v>
       </c>
       <c r="B8" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>129627015</v>
       </c>
       <c r="B9" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>129626741</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>129556174</v>
       </c>
       <c r="B3" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>129568972</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>129569041</v>
       </c>
       <c r="B5" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>129569006</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>129568991</v>
       </c>
       <c r="B7" t="n">
-        <v>58100</v>
+        <v>58105</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>129626512</v>
       </c>
       <c r="B8" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>129627015</v>
       </c>
       <c r="B9" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>129626741</v>
       </c>
       <c r="B10" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,7 +792,7 @@
         <v>129556174</v>
       </c>
       <c r="B3" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,57 +906,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129568972</v>
+        <v>129569041</v>
       </c>
       <c r="B4" t="n">
-        <v>57732</v>
+        <v>100958</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Dyveln, Härserud, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>347300</v>
+        <v>347267</v>
       </c>
       <c r="R4" t="n">
-        <v>6542773</v>
+        <v>6542704</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -991,43 +987,19 @@
           <t>2025-11-06</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska rejäla hackspår i en stående död gran. På fyndplatsen finns rikligt med stående död ved av gran.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1045,53 +1017,57 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129569041</v>
+        <v>129568972</v>
       </c>
       <c r="B5" t="n">
-        <v>100957</v>
+        <v>57733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dyveln, Härserud, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>347267</v>
+        <v>347300</v>
       </c>
       <c r="R5" t="n">
-        <v>6542704</v>
+        <v>6542773</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1126,19 +1102,43 @@
           <t>2025-11-06</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska rejäla hackspår i en stående död gran. På fyndplatsen finns rikligt med stående död ved av gran.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1159,7 +1159,7 @@
         <v>129569006</v>
       </c>
       <c r="B6" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>129568991</v>
       </c>
       <c r="B7" t="n">
-        <v>58105</v>
+        <v>58106</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>129626512</v>
       </c>
       <c r="B8" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>129627015</v>
       </c>
       <c r="B9" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>129626741</v>
       </c>
       <c r="B10" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1815,6 +1815,2899 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129774308</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91552</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ebberud, Dls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>347310</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6542827</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129774294</v>
+      </c>
+      <c r="B12" t="n">
+        <v>96094</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ebberud, Dls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>347444</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6542658</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129774319</v>
+      </c>
+      <c r="B13" t="n">
+        <v>75188</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ebberud, Dls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>347357</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6542883</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129774300</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91588</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ebberud, Dls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>347399</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6542733</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129774302</v>
+      </c>
+      <c r="B15" t="n">
+        <v>75188</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ebberud, Dls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>347301</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6542777</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129774350</v>
+      </c>
+      <c r="B16" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ebberud, Dls</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>347378</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6542728</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129774306</v>
+      </c>
+      <c r="B17" t="n">
+        <v>75188</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ebberud, Dls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>347301</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6542822</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129774307</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91645</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5321</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Barkticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Oxyporus corticola</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ebberud, Dls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>347300</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6542825</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129774313</v>
+      </c>
+      <c r="B19" t="n">
+        <v>75188</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ebberud, Dls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>347308</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6542855</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129774351</v>
+      </c>
+      <c r="B20" t="n">
+        <v>100958</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ebberud, Dls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>347223</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6542771</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129774349</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97015</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>53</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ebberud, Dls</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>347416</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6542737</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129774316</v>
+      </c>
+      <c r="B22" t="n">
+        <v>97015</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>53</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ebberud, Dls</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>347321</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6542862</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129774315</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91602</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Ebberud, Dls</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>347320</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6542863</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129774314</v>
+      </c>
+      <c r="B24" t="n">
+        <v>75188</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Ebberud, Dls</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>347318</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6542859</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129774299</v>
+      </c>
+      <c r="B25" t="n">
+        <v>4773</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Ebberud, Dls</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>347399</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6542733</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129774312</v>
+      </c>
+      <c r="B26" t="n">
+        <v>4773</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Ebberud, Dls</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>347308</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6542855</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129774311</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91552</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Ebberud, Dls</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>347308</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6542847</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129774304</v>
+      </c>
+      <c r="B28" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Ebberud, Dls</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>347317</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6542803</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129774318</v>
+      </c>
+      <c r="B29" t="n">
+        <v>4773</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Ebberud, Dls</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>347344</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6542868</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129774298</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91552</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Ebberud, Dls</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>347493</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6542818</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129774296</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91552</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Ebberud, Dls</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>347491</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6542739</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129774295</v>
+      </c>
+      <c r="B32" t="n">
+        <v>75188</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Ebberud, Dls</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>347491</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6542667</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129774301</v>
+      </c>
+      <c r="B33" t="n">
+        <v>75188</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Ebberud, Dls</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>347363</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6542755</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129774303</v>
+      </c>
+      <c r="B34" t="n">
+        <v>97015</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>53</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Ebberud, Dls</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>347296</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6542789</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129774317</v>
+      </c>
+      <c r="B35" t="n">
+        <v>75188</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Ebberud, Dls</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>347338</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6542853</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129774305</v>
+      </c>
+      <c r="B36" t="n">
+        <v>4773</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Ebberud, Dls</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>347314</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6542809</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -906,53 +906,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129569041</v>
+        <v>129568972</v>
       </c>
       <c r="B4" t="n">
-        <v>100958</v>
+        <v>57733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Dyveln, Härserud, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>347267</v>
+        <v>347300</v>
       </c>
       <c r="R4" t="n">
-        <v>6542704</v>
+        <v>6542773</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -987,19 +991,43 @@
           <t>2025-11-06</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska rejäla hackspår i en stående död gran. På fyndplatsen finns rikligt med stående död ved av gran.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1017,57 +1045,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129568972</v>
+        <v>129569041</v>
       </c>
       <c r="B5" t="n">
-        <v>57733</v>
+        <v>100958</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dyveln, Härserud, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>347300</v>
+        <v>347267</v>
       </c>
       <c r="R5" t="n">
-        <v>6542773</v>
+        <v>6542704</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1102,43 +1126,19 @@
           <t>2025-11-06</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska rejäla hackspår i en stående död gran. På fyndplatsen finns rikligt med stående död ved av gran.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>129556174</v>
       </c>
       <c r="B3" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>129569041</v>
       </c>
       <c r="B5" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>129626512</v>
       </c>
       <c r="B8" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>129626741</v>
       </c>
       <c r="B10" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>129774308</v>
       </c>
       <c r="B11" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>129774294</v>
       </c>
       <c r="B12" t="n">
-        <v>96094</v>
+        <v>96099</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>129774319</v>
       </c>
       <c r="B13" t="n">
-        <v>75188</v>
+        <v>75193</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>129774300</v>
       </c>
       <c r="B14" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>129774302</v>
       </c>
       <c r="B15" t="n">
-        <v>75188</v>
+        <v>75193</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2362,10 +2362,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129774350</v>
+        <v>129774306</v>
       </c>
       <c r="B16" t="n">
-        <v>5197</v>
+        <v>75193</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,39 +2373,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>105930</v>
+        <v>6426</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>347378</v>
+        <v>347301</v>
       </c>
       <c r="R16" t="n">
-        <v>6542728</v>
+        <v>6542822</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2479,10 +2474,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129774306</v>
+        <v>129774350</v>
       </c>
       <c r="B17" t="n">
-        <v>75188</v>
+        <v>5197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2490,34 +2485,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6426</v>
+        <v>105930</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>347301</v>
+        <v>347378</v>
       </c>
       <c r="R17" t="n">
-        <v>6542822</v>
+        <v>6542728</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2591,10 +2591,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129774307</v>
+        <v>129774313</v>
       </c>
       <c r="B18" t="n">
-        <v>91645</v>
+        <v>75193</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2602,21 +2602,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5321</v>
+        <v>6426</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>347300</v>
+        <v>347308</v>
       </c>
       <c r="R18" t="n">
-        <v>6542825</v>
+        <v>6542855</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2670,23 +2670,22 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2704,10 +2703,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129774313</v>
+        <v>129774307</v>
       </c>
       <c r="B19" t="n">
-        <v>75188</v>
+        <v>91650</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2715,21 +2714,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6426</v>
+        <v>5321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2739,10 +2738,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>347308</v>
+        <v>347300</v>
       </c>
       <c r="R19" t="n">
-        <v>6542855</v>
+        <v>6542825</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2783,22 +2782,23 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2819,7 +2819,7 @@
         <v>129774351</v>
       </c>
       <c r="B20" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>129774349</v>
       </c>
       <c r="B21" t="n">
-        <v>97015</v>
+        <v>97020</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>129774316</v>
       </c>
       <c r="B22" t="n">
-        <v>97015</v>
+        <v>97020</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>129774315</v>
       </c>
       <c r="B23" t="n">
-        <v>91602</v>
+        <v>91607</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>129774314</v>
       </c>
       <c r="B24" t="n">
-        <v>75188</v>
+        <v>75193</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>129774311</v>
       </c>
       <c r="B27" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>129774298</v>
       </c>
       <c r="B30" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>129774296</v>
       </c>
       <c r="B31" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>129774295</v>
       </c>
       <c r="B32" t="n">
-        <v>75188</v>
+        <v>75193</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>129774301</v>
       </c>
       <c r="B33" t="n">
-        <v>75188</v>
+        <v>75193</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>129774303</v>
       </c>
       <c r="B34" t="n">
-        <v>97015</v>
+        <v>97020</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>129774317</v>
       </c>
       <c r="B35" t="n">
-        <v>75188</v>
+        <v>75193</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -906,57 +906,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129568972</v>
+        <v>129569041</v>
       </c>
       <c r="B4" t="n">
-        <v>57733</v>
+        <v>100963</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Dyveln, Härserud, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>347300</v>
+        <v>347267</v>
       </c>
       <c r="R4" t="n">
-        <v>6542773</v>
+        <v>6542704</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -991,43 +987,19 @@
           <t>2025-11-06</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska rejäla hackspår i en stående död gran. På fyndplatsen finns rikligt med stående död ved av gran.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1045,53 +1017,57 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129569041</v>
+        <v>129568972</v>
       </c>
       <c r="B5" t="n">
-        <v>100963</v>
+        <v>57733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dyveln, Härserud, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>347267</v>
+        <v>347300</v>
       </c>
       <c r="R5" t="n">
-        <v>6542704</v>
+        <v>6542773</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1126,19 +1102,43 @@
           <t>2025-11-06</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska rejäla hackspår i en stående död gran. På fyndplatsen finns rikligt med stående död ved av gran.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1817,10 +1817,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129774308</v>
+        <v>129774319</v>
       </c>
       <c r="B11" t="n">
-        <v>91557</v>
+        <v>75193</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1828,21 +1828,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>347310</v>
+        <v>347357</v>
       </c>
       <c r="R11" t="n">
-        <v>6542827</v>
+        <v>6542883</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129774294</v>
+        <v>129774308</v>
       </c>
       <c r="B12" t="n">
-        <v>96099</v>
+        <v>91557</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1940,21 +1940,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2667</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>347444</v>
+        <v>347310</v>
       </c>
       <c r="R12" t="n">
-        <v>6542658</v>
+        <v>6542827</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2010,6 +2010,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2026,10 +2041,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129774319</v>
+        <v>129774294</v>
       </c>
       <c r="B13" t="n">
-        <v>75193</v>
+        <v>96099</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,21 +2052,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6426</v>
+        <v>2667</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2061,10 +2076,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>347357</v>
+        <v>347444</v>
       </c>
       <c r="R13" t="n">
-        <v>6542883</v>
+        <v>6542658</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2107,21 +2122,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2591,10 +2591,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129774313</v>
+        <v>129774307</v>
       </c>
       <c r="B18" t="n">
-        <v>75193</v>
+        <v>91650</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2602,21 +2602,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6426</v>
+        <v>5321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>347308</v>
+        <v>347300</v>
       </c>
       <c r="R18" t="n">
-        <v>6542855</v>
+        <v>6542825</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2670,22 +2670,23 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2703,10 +2704,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129774307</v>
+        <v>129774313</v>
       </c>
       <c r="B19" t="n">
-        <v>91650</v>
+        <v>75193</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2714,21 +2715,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5321</v>
+        <v>6426</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2738,10 +2739,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>347300</v>
+        <v>347308</v>
       </c>
       <c r="R19" t="n">
-        <v>6542825</v>
+        <v>6542855</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2782,23 +2783,22 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -906,53 +906,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129569041</v>
+        <v>129568972</v>
       </c>
       <c r="B4" t="n">
-        <v>100963</v>
+        <v>57733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Dyveln, Härserud, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>347267</v>
+        <v>347300</v>
       </c>
       <c r="R4" t="n">
-        <v>6542704</v>
+        <v>6542773</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -987,19 +991,43 @@
           <t>2025-11-06</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska rejäla hackspår i en stående död gran. På fyndplatsen finns rikligt med stående död ved av gran.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1017,57 +1045,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129568972</v>
+        <v>129569041</v>
       </c>
       <c r="B5" t="n">
-        <v>57733</v>
+        <v>100963</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dyveln, Härserud, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>347300</v>
+        <v>347267</v>
       </c>
       <c r="R5" t="n">
-        <v>6542773</v>
+        <v>6542704</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1102,43 +1126,19 @@
           <t>2025-11-06</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska rejäla hackspår i en stående död gran. På fyndplatsen finns rikligt med stående död ved av gran.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -2138,32 +2138,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129774300</v>
+        <v>129774302</v>
       </c>
       <c r="B14" t="n">
-        <v>91593</v>
+        <v>75193</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>347399</v>
+        <v>347301</v>
       </c>
       <c r="R14" t="n">
-        <v>6542733</v>
+        <v>6542777</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2250,32 +2250,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129774302</v>
+        <v>129774300</v>
       </c>
       <c r="B15" t="n">
-        <v>75193</v>
+        <v>91593</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>347301</v>
+        <v>347399</v>
       </c>
       <c r="R15" t="n">
-        <v>6542777</v>
+        <v>6542733</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -1817,10 +1817,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129774319</v>
+        <v>129774308</v>
       </c>
       <c r="B11" t="n">
-        <v>75193</v>
+        <v>91557</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1828,21 +1828,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>347357</v>
+        <v>347310</v>
       </c>
       <c r="R11" t="n">
-        <v>6542883</v>
+        <v>6542827</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129774308</v>
+        <v>129774294</v>
       </c>
       <c r="B12" t="n">
-        <v>91557</v>
+        <v>96099</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1940,21 +1940,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>2667</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>347310</v>
+        <v>347444</v>
       </c>
       <c r="R12" t="n">
-        <v>6542827</v>
+        <v>6542658</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2010,21 +2010,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2041,10 +2026,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129774294</v>
+        <v>129774319</v>
       </c>
       <c r="B13" t="n">
-        <v>96099</v>
+        <v>75193</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2052,21 +2037,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2667</v>
+        <v>6426</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2076,10 +2061,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>347444</v>
+        <v>347357</v>
       </c>
       <c r="R13" t="n">
-        <v>6542658</v>
+        <v>6542883</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2122,6 +2107,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2138,32 +2138,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129774302</v>
+        <v>129774300</v>
       </c>
       <c r="B14" t="n">
-        <v>75193</v>
+        <v>91593</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>347301</v>
+        <v>347399</v>
       </c>
       <c r="R14" t="n">
-        <v>6542777</v>
+        <v>6542733</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2250,32 +2250,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129774300</v>
+        <v>129774302</v>
       </c>
       <c r="B15" t="n">
-        <v>91593</v>
+        <v>75193</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>347399</v>
+        <v>347301</v>
       </c>
       <c r="R15" t="n">
-        <v>6542733</v>
+        <v>6542777</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2362,10 +2362,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129774306</v>
+        <v>129774350</v>
       </c>
       <c r="B16" t="n">
-        <v>75193</v>
+        <v>5197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,34 +2373,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6426</v>
+        <v>105930</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>347301</v>
+        <v>347378</v>
       </c>
       <c r="R16" t="n">
-        <v>6542822</v>
+        <v>6542728</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2474,10 +2479,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129774350</v>
+        <v>129774306</v>
       </c>
       <c r="B17" t="n">
-        <v>5197</v>
+        <v>75193</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2485,39 +2490,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>105930</v>
+        <v>6426</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>347378</v>
+        <v>347301</v>
       </c>
       <c r="R17" t="n">
-        <v>6542728</v>
+        <v>6542822</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2591,10 +2591,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129774307</v>
+        <v>129774313</v>
       </c>
       <c r="B18" t="n">
-        <v>91650</v>
+        <v>75193</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2602,21 +2602,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5321</v>
+        <v>6426</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>347300</v>
+        <v>347308</v>
       </c>
       <c r="R18" t="n">
-        <v>6542825</v>
+        <v>6542855</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2670,23 +2670,22 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2704,10 +2703,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129774313</v>
+        <v>129774307</v>
       </c>
       <c r="B19" t="n">
-        <v>75193</v>
+        <v>91650</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2715,21 +2714,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6426</v>
+        <v>5321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2739,10 +2738,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>347308</v>
+        <v>347300</v>
       </c>
       <c r="R19" t="n">
-        <v>6542855</v>
+        <v>6542825</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2783,22 +2782,23 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2913,10 +2913,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129774349</v>
+        <v>129774315</v>
       </c>
       <c r="B21" t="n">
-        <v>97020</v>
+        <v>91607</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2924,21 +2924,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>1204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2948,10 +2948,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>347416</v>
+        <v>347320</v>
       </c>
       <c r="R21" t="n">
-        <v>6542737</v>
+        <v>6542863</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2997,17 +2997,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3025,7 +3025,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129774316</v>
+        <v>129774349</v>
       </c>
       <c r="B22" t="n">
         <v>97020</v>
@@ -3060,10 +3060,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>347321</v>
+        <v>347416</v>
       </c>
       <c r="R22" t="n">
-        <v>6542862</v>
+        <v>6542737</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3109,17 +3109,17 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3137,10 +3137,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129774315</v>
+        <v>129774316</v>
       </c>
       <c r="B23" t="n">
-        <v>91607</v>
+        <v>97020</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3148,21 +3148,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3172,10 +3172,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>347320</v>
+        <v>347321</v>
       </c>
       <c r="R23" t="n">
-        <v>6542863</v>
+        <v>6542862</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>129556174</v>
       </c>
       <c r="B3" t="n">
-        <v>100963</v>
+        <v>100967</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,57 +906,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129568972</v>
+        <v>129569041</v>
       </c>
       <c r="B4" t="n">
-        <v>57733</v>
+        <v>100967</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Dyveln, Härserud, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>347300</v>
+        <v>347267</v>
       </c>
       <c r="R4" t="n">
-        <v>6542773</v>
+        <v>6542704</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -991,43 +987,19 @@
           <t>2025-11-06</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska rejäla hackspår i en stående död gran. På fyndplatsen finns rikligt med stående död ved av gran.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1045,53 +1017,57 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129569041</v>
+        <v>129568972</v>
       </c>
       <c r="B5" t="n">
-        <v>100963</v>
+        <v>57733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dyveln, Härserud, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>347267</v>
+        <v>347300</v>
       </c>
       <c r="R5" t="n">
-        <v>6542704</v>
+        <v>6542773</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1126,19 +1102,43 @@
           <t>2025-11-06</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska rejäla hackspår i en stående död gran. På fyndplatsen finns rikligt med stående död ved av gran.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1405,7 +1405,7 @@
         <v>129626512</v>
       </c>
       <c r="B8" t="n">
-        <v>100963</v>
+        <v>100967</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>129774308</v>
       </c>
       <c r="B11" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>129774294</v>
       </c>
       <c r="B12" t="n">
-        <v>96099</v>
+        <v>96103</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2138,32 +2138,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129774300</v>
+        <v>129774302</v>
       </c>
       <c r="B14" t="n">
-        <v>91593</v>
+        <v>75193</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>347399</v>
+        <v>347301</v>
       </c>
       <c r="R14" t="n">
-        <v>6542733</v>
+        <v>6542777</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2250,32 +2250,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129774302</v>
+        <v>129774300</v>
       </c>
       <c r="B15" t="n">
-        <v>75193</v>
+        <v>91597</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>347301</v>
+        <v>347399</v>
       </c>
       <c r="R15" t="n">
-        <v>6542777</v>
+        <v>6542733</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2362,10 +2362,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129774350</v>
+        <v>129774306</v>
       </c>
       <c r="B16" t="n">
-        <v>5197</v>
+        <v>75193</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,39 +2373,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>105930</v>
+        <v>6426</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>347378</v>
+        <v>347301</v>
       </c>
       <c r="R16" t="n">
-        <v>6542728</v>
+        <v>6542822</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2479,10 +2474,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129774306</v>
+        <v>129774350</v>
       </c>
       <c r="B17" t="n">
-        <v>75193</v>
+        <v>5197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2490,34 +2485,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6426</v>
+        <v>105930</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>347301</v>
+        <v>347378</v>
       </c>
       <c r="R17" t="n">
-        <v>6542822</v>
+        <v>6542728</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2591,10 +2591,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129774313</v>
+        <v>129774307</v>
       </c>
       <c r="B18" t="n">
-        <v>75193</v>
+        <v>91654</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2602,21 +2602,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6426</v>
+        <v>5321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>347308</v>
+        <v>347300</v>
       </c>
       <c r="R18" t="n">
-        <v>6542855</v>
+        <v>6542825</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2670,22 +2670,23 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2703,10 +2704,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129774307</v>
+        <v>129774313</v>
       </c>
       <c r="B19" t="n">
-        <v>91650</v>
+        <v>75193</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2714,21 +2715,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5321</v>
+        <v>6426</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2738,10 +2739,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>347300</v>
+        <v>347308</v>
       </c>
       <c r="R19" t="n">
-        <v>6542825</v>
+        <v>6542855</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2782,23 +2783,22 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2819,7 +2819,7 @@
         <v>129774351</v>
       </c>
       <c r="B20" t="n">
-        <v>100963</v>
+        <v>100967</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2913,10 +2913,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129774315</v>
+        <v>129774349</v>
       </c>
       <c r="B21" t="n">
-        <v>91607</v>
+        <v>97024</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2924,21 +2924,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1204</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2948,10 +2948,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>347320</v>
+        <v>347416</v>
       </c>
       <c r="R21" t="n">
-        <v>6542863</v>
+        <v>6542737</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2997,17 +2997,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3025,10 +3025,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129774349</v>
+        <v>129774316</v>
       </c>
       <c r="B22" t="n">
-        <v>97020</v>
+        <v>97024</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3060,10 +3060,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>347416</v>
+        <v>347321</v>
       </c>
       <c r="R22" t="n">
-        <v>6542737</v>
+        <v>6542862</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3109,17 +3109,17 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3137,10 +3137,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129774316</v>
+        <v>129774315</v>
       </c>
       <c r="B23" t="n">
-        <v>97020</v>
+        <v>91611</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3148,21 +3148,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>1204</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3172,10 +3172,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>347321</v>
+        <v>347320</v>
       </c>
       <c r="R23" t="n">
-        <v>6542862</v>
+        <v>6542863</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3593,7 +3593,7 @@
         <v>129774311</v>
       </c>
       <c r="B27" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>129774298</v>
       </c>
       <c r="B30" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>129774296</v>
       </c>
       <c r="B31" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129774295</v>
+        <v>129774301</v>
       </c>
       <c r="B32" t="n">
         <v>75193</v>
@@ -4195,10 +4195,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>347491</v>
+        <v>347363</v>
       </c>
       <c r="R32" t="n">
-        <v>6542667</v>
+        <v>6542755</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4272,7 +4272,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129774301</v>
+        <v>129774295</v>
       </c>
       <c r="B33" t="n">
         <v>75193</v>
@@ -4307,10 +4307,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>347363</v>
+        <v>347491</v>
       </c>
       <c r="R33" t="n">
-        <v>6542755</v>
+        <v>6542667</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4387,7 +4387,7 @@
         <v>129774303</v>
       </c>
       <c r="B34" t="n">
-        <v>97020</v>
+        <v>97024</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4481,10 +4481,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129774317</v>
+        <v>129774305</v>
       </c>
       <c r="B35" t="n">
-        <v>75193</v>
+        <v>4773</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4492,34 +4492,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6426</v>
+        <v>100299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>347338</v>
+        <v>347314</v>
       </c>
       <c r="R35" t="n">
-        <v>6542853</v>
+        <v>6542809</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4593,10 +4598,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129774305</v>
+        <v>129774317</v>
       </c>
       <c r="B36" t="n">
-        <v>4773</v>
+        <v>75193</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4604,39 +4609,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100299</v>
+        <v>6426</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>347314</v>
+        <v>347338</v>
       </c>
       <c r="R36" t="n">
-        <v>6542809</v>
+        <v>6542853</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>129556174</v>
       </c>
       <c r="B3" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>129569041</v>
       </c>
       <c r="B4" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>129626512</v>
       </c>
       <c r="B8" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>129774308</v>
       </c>
       <c r="B11" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>129774294</v>
       </c>
       <c r="B12" t="n">
-        <v>96103</v>
+        <v>96105</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2138,32 +2138,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129774302</v>
+        <v>129774300</v>
       </c>
       <c r="B14" t="n">
-        <v>75193</v>
+        <v>91599</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>347301</v>
+        <v>347399</v>
       </c>
       <c r="R14" t="n">
-        <v>6542777</v>
+        <v>6542733</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2250,32 +2250,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129774300</v>
+        <v>129774302</v>
       </c>
       <c r="B15" t="n">
-        <v>91597</v>
+        <v>75193</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>347399</v>
+        <v>347301</v>
       </c>
       <c r="R15" t="n">
-        <v>6542733</v>
+        <v>6542777</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2362,10 +2362,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129774306</v>
+        <v>129774350</v>
       </c>
       <c r="B16" t="n">
-        <v>75193</v>
+        <v>5197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,34 +2373,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6426</v>
+        <v>105930</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>347301</v>
+        <v>347378</v>
       </c>
       <c r="R16" t="n">
-        <v>6542822</v>
+        <v>6542728</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2474,10 +2479,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129774350</v>
+        <v>129774306</v>
       </c>
       <c r="B17" t="n">
-        <v>5197</v>
+        <v>75193</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2485,39 +2490,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>105930</v>
+        <v>6426</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>347378</v>
+        <v>347301</v>
       </c>
       <c r="R17" t="n">
-        <v>6542728</v>
+        <v>6542822</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2594,7 +2594,7 @@
         <v>129774307</v>
       </c>
       <c r="B18" t="n">
-        <v>91654</v>
+        <v>91656</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>129774351</v>
       </c>
       <c r="B20" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2913,10 +2913,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129774349</v>
+        <v>129774315</v>
       </c>
       <c r="B21" t="n">
-        <v>97024</v>
+        <v>91613</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2924,21 +2924,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>1204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2948,10 +2948,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>347416</v>
+        <v>347320</v>
       </c>
       <c r="R21" t="n">
-        <v>6542737</v>
+        <v>6542863</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2997,17 +2997,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3028,7 +3028,7 @@
         <v>129774316</v>
       </c>
       <c r="B22" t="n">
-        <v>97024</v>
+        <v>97026</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3137,10 +3137,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129774315</v>
+        <v>129774349</v>
       </c>
       <c r="B23" t="n">
-        <v>91611</v>
+        <v>97026</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3148,21 +3148,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3172,10 +3172,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>347320</v>
+        <v>347416</v>
       </c>
       <c r="R23" t="n">
-        <v>6542863</v>
+        <v>6542737</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3221,17 +3221,17 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3593,7 +3593,7 @@
         <v>129774311</v>
       </c>
       <c r="B27" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>129774298</v>
       </c>
       <c r="B30" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>129774296</v>
       </c>
       <c r="B31" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>129774303</v>
       </c>
       <c r="B34" t="n">
-        <v>97024</v>
+        <v>97026</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4481,10 +4481,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129774305</v>
+        <v>129774317</v>
       </c>
       <c r="B35" t="n">
-        <v>4773</v>
+        <v>75193</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4492,39 +4492,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100299</v>
+        <v>6426</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>347314</v>
+        <v>347338</v>
       </c>
       <c r="R35" t="n">
-        <v>6542809</v>
+        <v>6542853</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4598,10 +4593,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129774317</v>
+        <v>129774305</v>
       </c>
       <c r="B36" t="n">
-        <v>75193</v>
+        <v>4773</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4609,34 +4604,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6426</v>
+        <v>100299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>347338</v>
+        <v>347314</v>
       </c>
       <c r="R36" t="n">
-        <v>6542853</v>
+        <v>6542809</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -906,53 +906,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129569041</v>
+        <v>129568972</v>
       </c>
       <c r="B4" t="n">
-        <v>100969</v>
+        <v>57733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Dyveln, Härserud, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>347267</v>
+        <v>347300</v>
       </c>
       <c r="R4" t="n">
-        <v>6542704</v>
+        <v>6542773</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -987,19 +991,43 @@
           <t>2025-11-06</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska rejäla hackspår i en stående död gran. På fyndplatsen finns rikligt med stående död ved av gran.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1017,57 +1045,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129568972</v>
+        <v>129569041</v>
       </c>
       <c r="B5" t="n">
-        <v>57733</v>
+        <v>100969</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dyveln, Härserud, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>347300</v>
+        <v>347267</v>
       </c>
       <c r="R5" t="n">
-        <v>6542773</v>
+        <v>6542704</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1102,43 +1126,19 @@
           <t>2025-11-06</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska rejäla hackspår i en stående död gran. På fyndplatsen finns rikligt med stående död ved av gran.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -2913,10 +2913,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129774315</v>
+        <v>129774316</v>
       </c>
       <c r="B21" t="n">
-        <v>91613</v>
+        <v>97026</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2924,21 +2924,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1204</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2948,10 +2948,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>347320</v>
+        <v>347321</v>
       </c>
       <c r="R21" t="n">
-        <v>6542863</v>
+        <v>6542862</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3025,7 +3025,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129774316</v>
+        <v>129774349</v>
       </c>
       <c r="B22" t="n">
         <v>97026</v>
@@ -3060,10 +3060,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>347321</v>
+        <v>347416</v>
       </c>
       <c r="R22" t="n">
-        <v>6542862</v>
+        <v>6542737</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3109,17 +3109,17 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3137,10 +3137,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129774349</v>
+        <v>129774315</v>
       </c>
       <c r="B23" t="n">
-        <v>97026</v>
+        <v>91613</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3148,21 +3148,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>1204</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3172,10 +3172,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>347416</v>
+        <v>347320</v>
       </c>
       <c r="R23" t="n">
-        <v>6542737</v>
+        <v>6542863</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3221,17 +3221,17 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4708,6 +4708,632 @@
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129914761</v>
+      </c>
+      <c r="B37" t="n">
+        <v>91613</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Väst Krokvattnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>347570</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6542693</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Både äldre och yngre fruktkroppar</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Roger Gran, Anders Niklasson, Leif Appelgren, Roger Adolfsson, Martin Jentzen</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129914801</v>
+      </c>
+      <c r="B38" t="n">
+        <v>97032</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>53</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Väst Krokvattnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>347420</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6542738</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På tallåga i naturskog</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Roger Gran, Anders Niklasson, Leif Appelgren, Roger Adolfsson, Martin Jentzen</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129914872</v>
+      </c>
+      <c r="B39" t="n">
+        <v>97407</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Nordost Rudetjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>347259</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6542739</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Roger Gran, Anders Niklasson, Leif Appelgren, Roger Adolfsson, Martin Jentzen</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129914793</v>
+      </c>
+      <c r="B40" t="n">
+        <v>92919</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Väst Krokvattnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>347445</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6542787</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Roger Gran, Anders Niklasson, Leif Appelgren, Roger Adolfsson, Martin Jentzen</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129914838</v>
+      </c>
+      <c r="B41" t="n">
+        <v>91372</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Nordost Rudetjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>347253</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6542712</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Roger Gran, Anders Niklasson, Leif Appelgren, Roger Adolfsson, Martin Jentzen</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129914767</v>
+      </c>
+      <c r="B42" t="n">
+        <v>4773</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Väst Krokvattnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>347570</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6542693</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Roger Gran, Anders Niklasson, Leif Appelgren, Roger Adolfsson, Martin Jentzen</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>129556174</v>
       </c>
       <c r="B3" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>129569041</v>
       </c>
       <c r="B5" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>129626512</v>
       </c>
       <c r="B8" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1817,10 +1817,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129774308</v>
+        <v>129774319</v>
       </c>
       <c r="B11" t="n">
-        <v>91563</v>
+        <v>75193</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1828,21 +1828,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>347310</v>
+        <v>347357</v>
       </c>
       <c r="R11" t="n">
-        <v>6542827</v>
+        <v>6542883</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1932,7 +1932,7 @@
         <v>129774294</v>
       </c>
       <c r="B12" t="n">
-        <v>96105</v>
+        <v>96115</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129774319</v>
+        <v>129774308</v>
       </c>
       <c r="B13" t="n">
-        <v>75193</v>
+        <v>91563</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,21 +2037,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>347357</v>
+        <v>347310</v>
       </c>
       <c r="R13" t="n">
-        <v>6542883</v>
+        <v>6542827</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2138,32 +2138,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129774300</v>
+        <v>129774302</v>
       </c>
       <c r="B14" t="n">
-        <v>91599</v>
+        <v>75193</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>347399</v>
+        <v>347301</v>
       </c>
       <c r="R14" t="n">
-        <v>6542733</v>
+        <v>6542777</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2250,32 +2250,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129774302</v>
+        <v>129774300</v>
       </c>
       <c r="B15" t="n">
-        <v>75193</v>
+        <v>91599</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>347301</v>
+        <v>347399</v>
       </c>
       <c r="R15" t="n">
-        <v>6542777</v>
+        <v>6542733</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2362,10 +2362,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129774350</v>
+        <v>129774306</v>
       </c>
       <c r="B16" t="n">
-        <v>5197</v>
+        <v>75193</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,39 +2373,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>105930</v>
+        <v>6426</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>347378</v>
+        <v>347301</v>
       </c>
       <c r="R16" t="n">
-        <v>6542728</v>
+        <v>6542822</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2479,10 +2474,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129774306</v>
+        <v>129774350</v>
       </c>
       <c r="B17" t="n">
-        <v>75193</v>
+        <v>5197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2490,34 +2485,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6426</v>
+        <v>105930</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>347301</v>
+        <v>347378</v>
       </c>
       <c r="R17" t="n">
-        <v>6542822</v>
+        <v>6542728</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2819,7 +2819,7 @@
         <v>129774351</v>
       </c>
       <c r="B20" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2913,10 +2913,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129774316</v>
+        <v>129774349</v>
       </c>
       <c r="B21" t="n">
-        <v>97026</v>
+        <v>97036</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2948,10 +2948,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>347321</v>
+        <v>347416</v>
       </c>
       <c r="R21" t="n">
-        <v>6542862</v>
+        <v>6542737</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2997,17 +2997,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3025,10 +3025,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129774349</v>
+        <v>129774316</v>
       </c>
       <c r="B22" t="n">
-        <v>97026</v>
+        <v>97036</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3060,10 +3060,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>347416</v>
+        <v>347321</v>
       </c>
       <c r="R22" t="n">
-        <v>6542737</v>
+        <v>6542862</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3109,17 +3109,17 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -4387,7 +4387,7 @@
         <v>129774303</v>
       </c>
       <c r="B34" t="n">
-        <v>97026</v>
+        <v>97036</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4481,10 +4481,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129774317</v>
+        <v>129774305</v>
       </c>
       <c r="B35" t="n">
-        <v>75193</v>
+        <v>4773</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4492,34 +4492,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6426</v>
+        <v>100299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>347338</v>
+        <v>347314</v>
       </c>
       <c r="R35" t="n">
-        <v>6542853</v>
+        <v>6542809</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4593,10 +4598,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129774305</v>
+        <v>129774317</v>
       </c>
       <c r="B36" t="n">
-        <v>4773</v>
+        <v>75193</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4604,39 +4609,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100299</v>
+        <v>6426</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>347314</v>
+        <v>347338</v>
       </c>
       <c r="R36" t="n">
-        <v>6542809</v>
+        <v>6542853</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4818,7 +4818,7 @@
         <v>129914801</v>
       </c>
       <c r="B38" t="n">
-        <v>97032</v>
+        <v>97036</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         <v>129914872</v>
       </c>
       <c r="B39" t="n">
-        <v>97407</v>
+        <v>97411</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -1817,10 +1817,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129774319</v>
+        <v>129774294</v>
       </c>
       <c r="B11" t="n">
-        <v>75193</v>
+        <v>96115</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1828,21 +1828,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6426</v>
+        <v>2667</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>347357</v>
+        <v>347444</v>
       </c>
       <c r="R11" t="n">
-        <v>6542883</v>
+        <v>6542658</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1898,21 +1898,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1929,10 +1914,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129774294</v>
+        <v>129774319</v>
       </c>
       <c r="B12" t="n">
-        <v>96115</v>
+        <v>75193</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1940,21 +1925,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2667</v>
+        <v>6426</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1964,10 +1949,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>347444</v>
+        <v>347357</v>
       </c>
       <c r="R12" t="n">
-        <v>6542658</v>
+        <v>6542883</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2010,6 +1995,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2138,32 +2138,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129774302</v>
+        <v>129774300</v>
       </c>
       <c r="B14" t="n">
-        <v>75193</v>
+        <v>91599</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>347301</v>
+        <v>347399</v>
       </c>
       <c r="R14" t="n">
-        <v>6542777</v>
+        <v>6542733</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2250,32 +2250,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129774300</v>
+        <v>129774302</v>
       </c>
       <c r="B15" t="n">
-        <v>91599</v>
+        <v>75193</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>347399</v>
+        <v>347301</v>
       </c>
       <c r="R15" t="n">
-        <v>6542733</v>
+        <v>6542777</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -1817,10 +1817,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129774294</v>
+        <v>129774308</v>
       </c>
       <c r="B11" t="n">
-        <v>96115</v>
+        <v>91566</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1828,21 +1828,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2667</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>347444</v>
+        <v>347310</v>
       </c>
       <c r="R11" t="n">
-        <v>6542658</v>
+        <v>6542827</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1898,6 +1898,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1914,10 +1929,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129774319</v>
+        <v>129774294</v>
       </c>
       <c r="B12" t="n">
-        <v>75193</v>
+        <v>96119</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,21 +1940,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6426</v>
+        <v>2667</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1949,10 +1964,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>347357</v>
+        <v>347444</v>
       </c>
       <c r="R12" t="n">
-        <v>6542883</v>
+        <v>6542658</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1995,21 +2010,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2026,10 +2026,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129774308</v>
+        <v>129774319</v>
       </c>
       <c r="B13" t="n">
-        <v>91563</v>
+        <v>75196</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,21 +2037,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>347310</v>
+        <v>347357</v>
       </c>
       <c r="R13" t="n">
-        <v>6542827</v>
+        <v>6542883</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2138,32 +2138,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129774300</v>
+        <v>129774302</v>
       </c>
       <c r="B14" t="n">
-        <v>91599</v>
+        <v>75196</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>347399</v>
+        <v>347301</v>
       </c>
       <c r="R14" t="n">
-        <v>6542733</v>
+        <v>6542777</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2250,32 +2250,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129774302</v>
+        <v>129774300</v>
       </c>
       <c r="B15" t="n">
-        <v>75193</v>
+        <v>91602</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>347301</v>
+        <v>347399</v>
       </c>
       <c r="R15" t="n">
-        <v>6542777</v>
+        <v>6542733</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2365,7 +2365,7 @@
         <v>129774306</v>
       </c>
       <c r="B16" t="n">
-        <v>75193</v>
+        <v>75196</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2591,10 +2591,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129774307</v>
+        <v>129774313</v>
       </c>
       <c r="B18" t="n">
-        <v>91656</v>
+        <v>75196</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2602,21 +2602,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5321</v>
+        <v>6426</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>347300</v>
+        <v>347308</v>
       </c>
       <c r="R18" t="n">
-        <v>6542825</v>
+        <v>6542855</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2670,23 +2670,22 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2704,10 +2703,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129774313</v>
+        <v>129774307</v>
       </c>
       <c r="B19" t="n">
-        <v>75193</v>
+        <v>91659</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2715,21 +2714,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6426</v>
+        <v>5321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2739,10 +2738,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>347308</v>
+        <v>347300</v>
       </c>
       <c r="R19" t="n">
-        <v>6542855</v>
+        <v>6542825</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2783,22 +2782,23 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2819,7 +2819,7 @@
         <v>129774351</v>
       </c>
       <c r="B20" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2913,10 +2913,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129774349</v>
+        <v>129774316</v>
       </c>
       <c r="B21" t="n">
-        <v>97036</v>
+        <v>97040</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2948,10 +2948,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>347416</v>
+        <v>347321</v>
       </c>
       <c r="R21" t="n">
-        <v>6542737</v>
+        <v>6542862</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2997,17 +2997,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3025,10 +3025,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129774316</v>
+        <v>129774349</v>
       </c>
       <c r="B22" t="n">
-        <v>97036</v>
+        <v>97040</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3060,10 +3060,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>347321</v>
+        <v>347416</v>
       </c>
       <c r="R22" t="n">
-        <v>6542862</v>
+        <v>6542737</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3109,17 +3109,17 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3140,7 +3140,7 @@
         <v>129774315</v>
       </c>
       <c r="B23" t="n">
-        <v>91613</v>
+        <v>91616</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>129774314</v>
       </c>
       <c r="B24" t="n">
-        <v>75193</v>
+        <v>75196</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>129774311</v>
       </c>
       <c r="B27" t="n">
-        <v>91563</v>
+        <v>91566</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>129774298</v>
       </c>
       <c r="B30" t="n">
-        <v>91563</v>
+        <v>91566</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>129774296</v>
       </c>
       <c r="B31" t="n">
-        <v>91563</v>
+        <v>91566</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4160,10 +4160,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129774301</v>
+        <v>129774295</v>
       </c>
       <c r="B32" t="n">
-        <v>75193</v>
+        <v>75196</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4195,10 +4195,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>347363</v>
+        <v>347491</v>
       </c>
       <c r="R32" t="n">
-        <v>6542755</v>
+        <v>6542667</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4272,10 +4272,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129774295</v>
+        <v>129774301</v>
       </c>
       <c r="B33" t="n">
-        <v>75193</v>
+        <v>75196</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4307,10 +4307,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>347491</v>
+        <v>347363</v>
       </c>
       <c r="R33" t="n">
-        <v>6542667</v>
+        <v>6542755</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4387,7 +4387,7 @@
         <v>129774303</v>
       </c>
       <c r="B34" t="n">
-        <v>97036</v>
+        <v>97040</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>129774317</v>
       </c>
       <c r="B36" t="n">
-        <v>75193</v>
+        <v>75196</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>129914761</v>
       </c>
       <c r="B37" t="n">
-        <v>91613</v>
+        <v>91616</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Roger Gran, Anders Niklasson, Leif Appelgren, Roger Adolfsson, Martin Jentzen</t>
+          <t>Roger Gran, Martin Jentzen, Roger Adolfsson, Leif Appelgren, Anders Niklasson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4818,7 +4818,7 @@
         <v>129914801</v>
       </c>
       <c r="B38" t="n">
-        <v>97036</v>
+        <v>97040</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Roger Gran, Anders Niklasson, Leif Appelgren, Roger Adolfsson, Martin Jentzen</t>
+          <t>Roger Gran, Martin Jentzen, Roger Adolfsson, Leif Appelgren, Anders Niklasson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4924,7 +4924,7 @@
         <v>129914872</v>
       </c>
       <c r="B39" t="n">
-        <v>97411</v>
+        <v>97415</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>129914793</v>
       </c>
       <c r="B40" t="n">
-        <v>92919</v>
+        <v>92922</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Roger Gran, Anders Niklasson, Leif Appelgren, Roger Adolfsson, Martin Jentzen</t>
+          <t>Roger Gran, Martin Jentzen, Roger Adolfsson, Leif Appelgren, Anders Niklasson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5133,7 +5133,7 @@
         <v>129914838</v>
       </c>
       <c r="B41" t="n">
-        <v>91372</v>
+        <v>91375</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Roger Gran, Anders Niklasson, Leif Appelgren, Roger Adolfsson, Martin Jentzen</t>
+          <t>Roger Gran, Martin Jentzen, Roger Adolfsson, Leif Appelgren, Anders Niklasson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5329,7 +5329,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Roger Gran, Anders Niklasson, Leif Appelgren, Roger Adolfsson, Martin Jentzen</t>
+          <t>Roger Gran, Martin Jentzen, Roger Adolfsson, Leif Appelgren, Anders Niklasson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>129556174</v>
       </c>
       <c r="B3" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>129568972</v>
       </c>
       <c r="B4" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>129569041</v>
       </c>
       <c r="B5" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>129569006</v>
       </c>
       <c r="B6" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>129568991</v>
       </c>
       <c r="B7" t="n">
-        <v>58106</v>
+        <v>58108</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>129626512</v>
       </c>
       <c r="B8" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>129627015</v>
       </c>
       <c r="B9" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>129626741</v>
       </c>
       <c r="B10" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2138,32 +2138,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129774302</v>
+        <v>129774300</v>
       </c>
       <c r="B14" t="n">
-        <v>75196</v>
+        <v>91602</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>347301</v>
+        <v>347399</v>
       </c>
       <c r="R14" t="n">
-        <v>6542777</v>
+        <v>6542733</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2250,32 +2250,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129774300</v>
+        <v>129774302</v>
       </c>
       <c r="B15" t="n">
-        <v>91602</v>
+        <v>75196</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>347399</v>
+        <v>347301</v>
       </c>
       <c r="R15" t="n">
-        <v>6542733</v>
+        <v>6542777</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2591,10 +2591,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129774313</v>
+        <v>129774307</v>
       </c>
       <c r="B18" t="n">
-        <v>75196</v>
+        <v>91659</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2602,21 +2602,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6426</v>
+        <v>5321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>347308</v>
+        <v>347300</v>
       </c>
       <c r="R18" t="n">
-        <v>6542855</v>
+        <v>6542825</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2670,22 +2670,23 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2703,10 +2704,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129774307</v>
+        <v>129774313</v>
       </c>
       <c r="B19" t="n">
-        <v>91659</v>
+        <v>75196</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2714,21 +2715,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5321</v>
+        <v>6426</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2738,10 +2739,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>347300</v>
+        <v>347308</v>
       </c>
       <c r="R19" t="n">
-        <v>6542825</v>
+        <v>6542855</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2782,23 +2783,22 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2913,7 +2913,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129774316</v>
+        <v>129774349</v>
       </c>
       <c r="B21" t="n">
         <v>97040</v>
@@ -2948,10 +2948,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>347321</v>
+        <v>347416</v>
       </c>
       <c r="R21" t="n">
-        <v>6542862</v>
+        <v>6542737</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2997,17 +2997,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3025,7 +3025,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129774349</v>
+        <v>129774316</v>
       </c>
       <c r="B22" t="n">
         <v>97040</v>
@@ -3060,10 +3060,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>347416</v>
+        <v>347321</v>
       </c>
       <c r="R22" t="n">
-        <v>6542737</v>
+        <v>6542862</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3109,17 +3109,17 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -4160,7 +4160,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129774295</v>
+        <v>129774301</v>
       </c>
       <c r="B32" t="n">
         <v>75196</v>
@@ -4195,10 +4195,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>347491</v>
+        <v>347363</v>
       </c>
       <c r="R32" t="n">
-        <v>6542667</v>
+        <v>6542755</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4272,7 +4272,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129774301</v>
+        <v>129774295</v>
       </c>
       <c r="B33" t="n">
         <v>75196</v>
@@ -4307,10 +4307,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>347363</v>
+        <v>347491</v>
       </c>
       <c r="R33" t="n">
-        <v>6542755</v>
+        <v>6542667</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4808,7 +4808,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Roger Gran, Martin Jentzen, Roger Adolfsson, Leif Appelgren, Anders Niklasson</t>
+          <t>Roger Gran, Anders Niklasson, Leif Appelgren, Roger Adolfsson, Martin Jentzen</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Roger Gran, Martin Jentzen, Roger Adolfsson, Leif Appelgren, Anders Niklasson</t>
+          <t>Roger Gran, Anders Niklasson, Leif Appelgren, Roger Adolfsson, Martin Jentzen</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Roger Gran, Martin Jentzen, Roger Adolfsson, Leif Appelgren, Anders Niklasson</t>
+          <t>Roger Gran, Anders Niklasson, Leif Appelgren, Roger Adolfsson, Martin Jentzen</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5223,7 +5223,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Roger Gran, Martin Jentzen, Roger Adolfsson, Leif Appelgren, Anders Niklasson</t>
+          <t>Roger Gran, Anders Niklasson, Leif Appelgren, Roger Adolfsson, Martin Jentzen</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5329,7 +5329,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Roger Gran, Martin Jentzen, Roger Adolfsson, Leif Appelgren, Anders Niklasson</t>
+          <t>Roger Gran, Anders Niklasson, Leif Appelgren, Roger Adolfsson, Martin Jentzen</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -2362,10 +2362,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129774350</v>
+        <v>129774306</v>
       </c>
       <c r="B16" t="n">
-        <v>5197</v>
+        <v>75201</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,39 +2373,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>105930</v>
+        <v>6426</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>347378</v>
+        <v>347301</v>
       </c>
       <c r="R16" t="n">
-        <v>6542728</v>
+        <v>6542822</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2479,10 +2474,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129774306</v>
+        <v>129774350</v>
       </c>
       <c r="B17" t="n">
-        <v>75201</v>
+        <v>5197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2490,34 +2485,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6426</v>
+        <v>105930</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>347301</v>
+        <v>347378</v>
       </c>
       <c r="R17" t="n">
-        <v>6542822</v>
+        <v>6542728</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -4713,7 +4713,7 @@
         <v>129914761</v>
       </c>
       <c r="B37" t="n">
-        <v>91653</v>
+        <v>91655</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>129914801</v>
       </c>
       <c r="B38" t="n">
-        <v>97077</v>
+        <v>97079</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         <v>129914872</v>
       </c>
       <c r="B39" t="n">
-        <v>97452</v>
+        <v>97454</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>129914793</v>
       </c>
       <c r="B40" t="n">
-        <v>92959</v>
+        <v>92961</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         <v>129914838</v>
       </c>
       <c r="B41" t="n">
-        <v>91412</v>
+        <v>91414</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -4713,7 +4713,7 @@
         <v>129914761</v>
       </c>
       <c r="B37" t="n">
-        <v>91655</v>
+        <v>91742</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>129914801</v>
       </c>
       <c r="B38" t="n">
-        <v>97079</v>
+        <v>97166</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         <v>129914872</v>
       </c>
       <c r="B39" t="n">
-        <v>97454</v>
+        <v>97541</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>129914793</v>
       </c>
       <c r="B40" t="n">
-        <v>92961</v>
+        <v>93048</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         <v>129914838</v>
       </c>
       <c r="B41" t="n">
-        <v>91414</v>
+        <v>91501</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -5558,10 +5558,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133641594</v>
+        <v>133641605</v>
       </c>
       <c r="B45" t="n">
-        <v>57162</v>
+        <v>97796</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5569,45 +5569,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100138</v>
+        <v>2569</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Krokvattnet, Dls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>347384</v>
+        <v>347321</v>
       </c>
       <c r="R45" t="n">
-        <v>6542740</v>
+        <v>6542863</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5636,7 +5628,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5646,7 +5638,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5673,10 +5665,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133641605</v>
+        <v>133641594</v>
       </c>
       <c r="B46" t="n">
-        <v>97796</v>
+        <v>57162</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5684,37 +5676,45 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2569</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Krokvattnet, Dls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>347321</v>
+        <v>347384</v>
       </c>
       <c r="R46" t="n">
-        <v>6542863</v>
+        <v>6542740</v>
       </c>
       <c r="S46" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6110,57 +6110,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133641585</v>
+        <v>133641591</v>
       </c>
       <c r="B50" t="n">
-        <v>5366</v>
+        <v>91923</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>101728</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Krokvattnet, Dls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>347542</v>
+        <v>347430</v>
       </c>
       <c r="R50" t="n">
-        <v>6542732</v>
+        <v>6542734</v>
       </c>
       <c r="S50" t="n">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6189,7 +6180,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6199,7 +6190,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6208,7 +6199,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6334,48 +6324,57 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133641591</v>
+        <v>133641585</v>
       </c>
       <c r="B52" t="n">
-        <v>91923</v>
+        <v>5366</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>101728</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Krokvattnet, Dls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>347430</v>
+        <v>347542</v>
       </c>
       <c r="R52" t="n">
-        <v>6542734</v>
+        <v>6542732</v>
       </c>
       <c r="S52" t="n">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6404,7 +6403,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6414,7 +6413,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6423,6 +6422,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6441,57 +6441,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133641588</v>
+        <v>133641593</v>
       </c>
       <c r="B53" t="n">
-        <v>4776</v>
+        <v>91960</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100299</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Krokvattnet, Dls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>347481</v>
+        <v>347390</v>
       </c>
       <c r="R53" t="n">
-        <v>6542656</v>
+        <v>6542746</v>
       </c>
       <c r="S53" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6520,7 +6511,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6530,7 +6521,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6557,48 +6548,57 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133641593</v>
+        <v>133641588</v>
       </c>
       <c r="B54" t="n">
-        <v>91960</v>
+        <v>4776</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>100299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Krokvattnet, Dls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>347390</v>
+        <v>347481</v>
       </c>
       <c r="R54" t="n">
-        <v>6542746</v>
+        <v>6542656</v>
       </c>
       <c r="S54" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6781,7 +6781,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133641604</v>
+        <v>133641587</v>
       </c>
       <c r="B56" t="n">
         <v>91923</v>
@@ -6816,13 +6816,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>347321</v>
+        <v>347531</v>
       </c>
       <c r="R56" t="n">
-        <v>6542863</v>
+        <v>6542681</v>
       </c>
       <c r="S56" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6888,7 +6888,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133641587</v>
+        <v>133641604</v>
       </c>
       <c r="B57" t="n">
         <v>91923</v>
@@ -6923,13 +6923,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>347531</v>
+        <v>347321</v>
       </c>
       <c r="R57" t="n">
-        <v>6542681</v>
+        <v>6542863</v>
       </c>
       <c r="S57" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -5339,7 +5339,7 @@
         <v>133641584</v>
       </c>
       <c r="B43" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5558,10 +5558,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133641605</v>
+        <v>133641594</v>
       </c>
       <c r="B45" t="n">
-        <v>97796</v>
+        <v>57162</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5569,37 +5569,45 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2569</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Krokvattnet, Dls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>347321</v>
+        <v>347384</v>
       </c>
       <c r="R45" t="n">
-        <v>6542863</v>
+        <v>6542740</v>
       </c>
       <c r="S45" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5628,7 +5636,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5638,7 +5646,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5665,10 +5673,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133641594</v>
+        <v>133641605</v>
       </c>
       <c r="B46" t="n">
-        <v>57162</v>
+        <v>97803</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5676,45 +5684,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100138</v>
+        <v>2569</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Krokvattnet, Dls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>347384</v>
+        <v>347321</v>
       </c>
       <c r="R46" t="n">
-        <v>6542740</v>
+        <v>6542863</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5899,7 +5899,7 @@
         <v>133641586</v>
       </c>
       <c r="B48" t="n">
-        <v>91923</v>
+        <v>91930</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         <v>133641592</v>
       </c>
       <c r="B49" t="n">
-        <v>97421</v>
+        <v>97428</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6110,48 +6110,57 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133641591</v>
+        <v>133641585</v>
       </c>
       <c r="B50" t="n">
-        <v>91923</v>
+        <v>5366</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>101728</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Krokvattnet, Dls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>347430</v>
+        <v>347542</v>
       </c>
       <c r="R50" t="n">
-        <v>6542734</v>
+        <v>6542732</v>
       </c>
       <c r="S50" t="n">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6180,7 +6189,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6190,7 +6199,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6199,6 +6208,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6220,7 +6230,7 @@
         <v>133641590</v>
       </c>
       <c r="B51" t="n">
-        <v>75454</v>
+        <v>75461</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6324,57 +6334,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133641585</v>
+        <v>133641591</v>
       </c>
       <c r="B52" t="n">
-        <v>5366</v>
+        <v>91930</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>101728</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Krokvattnet, Dls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>347542</v>
+        <v>347430</v>
       </c>
       <c r="R52" t="n">
-        <v>6542732</v>
+        <v>6542734</v>
       </c>
       <c r="S52" t="n">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6403,7 +6404,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6413,7 +6414,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6422,7 +6423,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6441,48 +6441,57 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133641593</v>
+        <v>133641588</v>
       </c>
       <c r="B53" t="n">
-        <v>91960</v>
+        <v>4776</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>100299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Krokvattnet, Dls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>347390</v>
+        <v>347481</v>
       </c>
       <c r="R53" t="n">
-        <v>6542746</v>
+        <v>6542656</v>
       </c>
       <c r="S53" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6511,7 +6520,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6521,7 +6530,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6548,57 +6557,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133641588</v>
+        <v>133641593</v>
       </c>
       <c r="B54" t="n">
-        <v>4776</v>
+        <v>91967</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100299</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Krokvattnet, Dls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>347481</v>
+        <v>347390</v>
       </c>
       <c r="R54" t="n">
-        <v>6542656</v>
+        <v>6542746</v>
       </c>
       <c r="S54" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6781,10 +6781,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133641587</v>
+        <v>133641604</v>
       </c>
       <c r="B56" t="n">
-        <v>91923</v>
+        <v>91930</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6816,13 +6816,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>347531</v>
+        <v>347321</v>
       </c>
       <c r="R56" t="n">
-        <v>6542681</v>
+        <v>6542863</v>
       </c>
       <c r="S56" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6888,10 +6888,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133641604</v>
+        <v>133641587</v>
       </c>
       <c r="B57" t="n">
-        <v>91923</v>
+        <v>91930</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6923,13 +6923,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>347321</v>
+        <v>347531</v>
       </c>
       <c r="R57" t="n">
-        <v>6542863</v>
+        <v>6542681</v>
       </c>
       <c r="S57" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AY73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>55840945</v>
+        <v>129774303</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ebberud V.om, Dls</t>
+          <t>Ebberud, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>347373.6963853929</v>
+        <v>347296</v>
       </c>
       <c r="R2" t="n">
-        <v>6542880.582456828</v>
+        <v>6542789</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-11-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-11-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,65 +760,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Niklasson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Niklasson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129556174</v>
+        <v>129774316</v>
       </c>
       <c r="B3" t="n">
-        <v>100983</v>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dyveln, Dyveln, Dls</t>
+          <t>Ebberud, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>347257</v>
+        <v>347321</v>
       </c>
       <c r="R3" t="n">
-        <v>6542720</v>
+        <v>6542862</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:09</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:09</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,30 +854,40 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129568972</v>
+        <v>129774347</v>
       </c>
       <c r="B4" t="n">
-        <v>57734</v>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,46 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Dyveln, Härserud, Dls</t>
+          <t>Ebberud, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>347300</v>
+        <v>347388</v>
       </c>
       <c r="R4" t="n">
-        <v>6542773</v>
+        <v>6542868</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -983,17 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska rejäla hackspår i en stående död gran. På fyndplatsen finns rikligt med stående död ved av gran.</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,94 +965,61 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129569041</v>
+        <v>129774349</v>
       </c>
       <c r="B5" t="n">
-        <v>100983</v>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Dyveln, Härserud, Dls</t>
+          <t>Ebberud, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>347267</v>
+        <v>347416</v>
       </c>
       <c r="R5" t="n">
-        <v>6542704</v>
+        <v>6542737</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1118,12 +1046,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,34 +1060,43 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129569006</v>
+        <v>129914801</v>
       </c>
       <c r="B6" t="n">
-        <v>57734</v>
+        <v>97358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1167,53 +1104,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Dyveln, Härserud, Dls</t>
+          <t>Väst Krokvattnet, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>347438</v>
+        <v>347420</v>
       </c>
       <c r="R6" t="n">
-        <v>6542735</v>
+        <v>6542738</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1237,17 +1162,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>En lockande spillkråka i en skog med gott om stående död ved och aspar lämpliga för bohål under kommande häckning.</t>
+          <t>På tallåga i naturskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,90 +1183,64 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Med gran, tall och inslag av asp, björk och rönn.</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Roger Gran, Anders Niklasson, Leif Appelgren, Roger Adolfsson, Martin Jentzen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129568991</v>
+        <v>133641592</v>
       </c>
       <c r="B7" t="n">
-        <v>58108</v>
+        <v>97435</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Dyveln, Härserud, Dls</t>
+          <t>Krokvattnet, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>347354</v>
+        <v>347424</v>
       </c>
       <c r="R7" t="n">
-        <v>6542779</v>
+        <v>6542742</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1365,12 +1264,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,78 +1290,61 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129626512</v>
+        <v>129774300</v>
       </c>
       <c r="B8" t="n">
-        <v>100986</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Dyveln, Dls</t>
+          <t>Ebberud, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>347285</v>
+        <v>347399</v>
       </c>
       <c r="R8" t="n">
-        <v>6542754</v>
+        <v>6542733</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1479,22 +1371,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1503,34 +1385,43 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129627015</v>
+        <v>133641593</v>
       </c>
       <c r="B9" t="n">
-        <v>57737</v>
+        <v>91974</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,49 +1429,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Dyveln, Dls</t>
+          <t>Krokvattnet, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>347315</v>
+        <v>347390</v>
       </c>
       <c r="R9" t="n">
-        <v>6542796</v>
+        <v>6542746</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1604,27 +1483,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre grova hackspår i stambasen av en död tall.</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1635,89 +1509,61 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129626741</v>
+        <v>129774315</v>
       </c>
       <c r="B10" t="n">
-        <v>79087</v>
+        <v>91923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Dyveln, Dls</t>
+          <t>Ebberud, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>347201</v>
+        <v>347320</v>
       </c>
       <c r="R10" t="n">
-        <v>6542792</v>
+        <v>6542863</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1744,27 +1590,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:02</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på grenar av en tall.</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1773,92 +1604,84 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129774308</v>
+        <v>129914761</v>
       </c>
       <c r="B11" t="n">
-        <v>91603</v>
+        <v>91923</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ebberud, Dls</t>
+          <t>Väst Krokvattnet, Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>347310</v>
+        <v>347570</v>
       </c>
       <c r="R11" t="n">
-        <v>6542827</v>
+        <v>6542693</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1882,12 +1705,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Både äldre och yngre fruktkroppar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1898,79 +1726,68 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran, Anders Niklasson, Leif Appelgren, Roger Adolfsson, Martin Jentzen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129774294</v>
+        <v>129914822</v>
       </c>
       <c r="B12" t="n">
-        <v>96156</v>
+        <v>97776</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2667</v>
+        <v>1590</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Dunmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Trichocolea tomentella</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ehrh.) Dumort.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ebberud, Dls</t>
+          <t>Nordost Rudetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>347444</v>
+        <v>347289</v>
       </c>
       <c r="R12" t="n">
-        <v>6542658</v>
+        <v>6542680</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1994,12 +1811,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Riklig förekomst i örtrikt källdråg/ravin.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2014,60 +1836,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran, Anders Niklasson, Leif Appelgren, Roger Adolfsson, Martin Jentzen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129774319</v>
+        <v>133641598</v>
       </c>
       <c r="B13" t="n">
-        <v>75201</v>
+        <v>97853</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6426</v>
+        <v>1590</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Dunmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Trichocolea tomentella</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ehrh.) Dumort.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ebberud, Dls</t>
+          <t>Krokvattnet, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>347357</v>
+        <v>347266</v>
       </c>
       <c r="R13" t="n">
-        <v>6542883</v>
+        <v>6542691</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2091,12 +1913,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2107,79 +1939,68 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129774300</v>
+        <v>129914872</v>
       </c>
       <c r="B14" t="n">
-        <v>91639</v>
+        <v>97733</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>2569</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ebberud, Dls</t>
+          <t>Nordost Rudetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>347399</v>
+        <v>347259</v>
       </c>
       <c r="R14" t="n">
-        <v>6542733</v>
+        <v>6542739</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2203,12 +2024,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2219,41 +2040,26 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran, Anders Niklasson, Leif Appelgren, Roger Adolfsson, Martin Jentzen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129774302</v>
+        <v>133641605</v>
       </c>
       <c r="B15" t="n">
-        <v>75201</v>
+        <v>97810</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,37 +2067,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6426</v>
+        <v>2569</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ebberud, Dls</t>
+          <t>Krokvattnet, Dls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>347301</v>
+        <v>347321</v>
       </c>
       <c r="R15" t="n">
-        <v>6542777</v>
+        <v>6542863</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2315,12 +2121,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2331,41 +2147,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129774306</v>
+        <v>129914902</v>
       </c>
       <c r="B16" t="n">
-        <v>75201</v>
+        <v>97394</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,37 +2174,41 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6426</v>
+        <v>2590</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ebberud, Dls</t>
+          <t>Norr Rudetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>347301</v>
+        <v>347195</v>
       </c>
       <c r="R16" t="n">
-        <v>6542822</v>
+        <v>6542721</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2427,12 +2232,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På murken stubbe i sumpskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2443,41 +2253,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran, Anders Niklasson, Leif Appelgren, Roger Adolfsson, Martin Jentzen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129774350</v>
+        <v>133641600</v>
       </c>
       <c r="B17" t="n">
-        <v>5197</v>
+        <v>97471</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2485,42 +2280,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>105930</v>
+        <v>2590</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ebberud, Dls</t>
+          <t>Krokvattnet, Dls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>347378</v>
+        <v>347190</v>
       </c>
       <c r="R17" t="n">
-        <v>6542728</v>
+        <v>6542724</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2544,12 +2334,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2560,41 +2360,26 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129774307</v>
+        <v>133641602</v>
       </c>
       <c r="B18" t="n">
-        <v>91696</v>
+        <v>97471</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2602,37 +2387,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5321</v>
+        <v>2590</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ebberud, Dls</t>
+          <t>Krokvattnet, Dls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>347300</v>
+        <v>347169</v>
       </c>
       <c r="R18" t="n">
-        <v>6542825</v>
+        <v>6542734</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2656,12 +2441,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2670,44 +2465,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129774313</v>
+        <v>129774294</v>
       </c>
       <c r="B19" t="n">
-        <v>75201</v>
+        <v>96437</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2715,21 +2494,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6426</v>
+        <v>2667</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2739,10 +2518,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>347308</v>
+        <v>347444</v>
       </c>
       <c r="R19" t="n">
-        <v>6542855</v>
+        <v>6542658</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2785,21 +2564,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2816,10 +2580,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129774351</v>
+        <v>129914896</v>
       </c>
       <c r="B20" t="n">
-        <v>101020</v>
+        <v>96459</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2827,37 +2591,41 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>2819</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Trind spretmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella striatella</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ebberud, Dls</t>
+          <t>Norr Rudetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>347223</v>
+        <v>347195</v>
       </c>
       <c r="R20" t="n">
-        <v>6542771</v>
+        <v>6542721</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2881,12 +2649,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På basen av klibbal i sumpskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2901,60 +2674,63 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran, Anders Niklasson, Leif Appelgren, Roger Adolfsson, Martin Jentzen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129774349</v>
+        <v>129914838</v>
       </c>
       <c r="B21" t="n">
-        <v>97077</v>
+        <v>91680</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>3215</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ebberud, Dls</t>
+          <t>Nordost Rudetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>347416</v>
+        <v>347253</v>
       </c>
       <c r="R21" t="n">
-        <v>6542737</v>
+        <v>6542712</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2978,12 +2754,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2994,63 +2770,48 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran, Anders Niklasson, Leif Appelgren, Roger Adolfsson, Martin Jentzen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129774316</v>
+        <v>129774293</v>
       </c>
       <c r="B22" t="n">
-        <v>97077</v>
+        <v>92632</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>3298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3060,10 +2821,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>347321</v>
+        <v>347395</v>
       </c>
       <c r="R22" t="n">
-        <v>6542862</v>
+        <v>6542658</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3137,32 +2898,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129774315</v>
+        <v>129774307</v>
       </c>
       <c r="B23" t="n">
-        <v>91653</v>
+        <v>91966</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>5321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3172,10 +2933,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>347320</v>
+        <v>347300</v>
       </c>
       <c r="R23" t="n">
-        <v>6542863</v>
+        <v>6542825</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3216,22 +2977,23 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3249,10 +3011,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129774314</v>
+        <v>129774344</v>
       </c>
       <c r="B24" t="n">
-        <v>75201</v>
+        <v>91966</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3260,21 +3022,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6426</v>
+        <v>5321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3284,10 +3046,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>347318</v>
+        <v>347432</v>
       </c>
       <c r="R24" t="n">
-        <v>6542859</v>
+        <v>6542899</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3328,22 +3090,23 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3361,48 +3124,51 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129774299</v>
+        <v>129914742</v>
       </c>
       <c r="B25" t="n">
-        <v>4773</v>
+        <v>91930</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100299</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ebberud, Dls</t>
+          <t>Väst Krokvattnet, Dls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>347399</v>
+        <v>347601</v>
       </c>
       <c r="R25" t="n">
-        <v>6542733</v>
+        <v>6542713</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3421,17 +3187,17 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Laxarby</t>
+          <t>Steneby</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3442,41 +3208,26 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran, Anders Niklasson, Leif Appelgren, Roger Adolfsson, Martin Jentzen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129774312</v>
+        <v>129774296</v>
       </c>
       <c r="B26" t="n">
-        <v>4773</v>
+        <v>91872</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3484,39 +3235,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100299</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>347308</v>
+        <v>347491</v>
       </c>
       <c r="R26" t="n">
-        <v>6542855</v>
+        <v>6542739</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3590,10 +3336,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129774311</v>
+        <v>129774298</v>
       </c>
       <c r="B27" t="n">
-        <v>91603</v>
+        <v>91872</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3625,10 +3371,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>347308</v>
+        <v>347493</v>
       </c>
       <c r="R27" t="n">
-        <v>6542847</v>
+        <v>6542818</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3702,10 +3448,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129774304</v>
+        <v>129774308</v>
       </c>
       <c r="B28" t="n">
-        <v>5197</v>
+        <v>91872</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3713,39 +3459,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>105930</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>347317</v>
+        <v>347310</v>
       </c>
       <c r="R28" t="n">
-        <v>6542803</v>
+        <v>6542827</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3819,10 +3560,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129774318</v>
+        <v>129774311</v>
       </c>
       <c r="B29" t="n">
-        <v>4773</v>
+        <v>91872</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3830,39 +3571,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100299</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>347344</v>
+        <v>347308</v>
       </c>
       <c r="R29" t="n">
-        <v>6542868</v>
+        <v>6542847</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3936,10 +3672,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129774298</v>
+        <v>133641586</v>
       </c>
       <c r="B30" t="n">
-        <v>91603</v>
+        <v>91937</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3967,17 +3703,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ebberud, Dls</t>
+          <t>Krokvattnet, Dls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>347493</v>
+        <v>347538</v>
       </c>
       <c r="R30" t="n">
-        <v>6542818</v>
+        <v>6542688</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4001,12 +3737,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4017,41 +3763,26 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129774296</v>
+        <v>133641587</v>
       </c>
       <c r="B31" t="n">
-        <v>91603</v>
+        <v>91937</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4079,17 +3810,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ebberud, Dls</t>
+          <t>Krokvattnet, Dls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>347491</v>
+        <v>347531</v>
       </c>
       <c r="R31" t="n">
-        <v>6542739</v>
+        <v>6542681</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4113,12 +3844,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4129,41 +3870,26 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129774295</v>
+        <v>133641591</v>
       </c>
       <c r="B32" t="n">
-        <v>75201</v>
+        <v>91937</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4171,37 +3897,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ebberud, Dls</t>
+          <t>Krokvattnet, Dls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>347491</v>
+        <v>347430</v>
       </c>
       <c r="R32" t="n">
-        <v>6542667</v>
+        <v>6542734</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4225,12 +3951,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4241,41 +3977,26 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129774301</v>
+        <v>133641604</v>
       </c>
       <c r="B33" t="n">
-        <v>75201</v>
+        <v>91937</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4283,37 +4004,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Ebberud, Dls</t>
+          <t>Krokvattnet, Dls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>347363</v>
+        <v>347321</v>
       </c>
       <c r="R33" t="n">
-        <v>6542755</v>
+        <v>6542863</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4337,12 +4058,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4353,41 +4084,26 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129774303</v>
+        <v>129914793</v>
       </c>
       <c r="B34" t="n">
-        <v>97077</v>
+        <v>93235</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4395,37 +4111,48 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>5966</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Ebberud, Dls</t>
+          <t>Väst Krokvattnet, Dls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>347296</v>
+        <v>347445</v>
       </c>
       <c r="R34" t="n">
-        <v>6542789</v>
+        <v>6542787</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4449,12 +4176,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4469,60 +4196,62 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran, Anders Niklasson, Leif Appelgren, Roger Adolfsson, Martin Jentzen</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129774317</v>
+        <v>55840945</v>
       </c>
       <c r="B35" t="n">
-        <v>75201</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Ebberud, Dls</t>
+          <t>Ebberud V.om, Dls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>347338</v>
+        <v>347374</v>
       </c>
       <c r="R35" t="n">
-        <v>6542853</v>
+        <v>6542881</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4546,12 +4275,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2015-11-18</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2015-11-18</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4562,81 +4291,64 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Anders Niklasson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Anders Niklasson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129774305</v>
+        <v>129626741</v>
       </c>
       <c r="B36" t="n">
-        <v>4773</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Ebberud, Dls</t>
+          <t>Dyveln, Dls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>347314</v>
+        <v>347201</v>
       </c>
       <c r="R36" t="n">
-        <v>6542809</v>
+        <v>6542792</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4663,12 +4375,27 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på grenar av en tall.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4677,43 +4404,54 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129914761</v>
+        <v>129774292</v>
       </c>
       <c r="B37" t="n">
-        <v>91742</v>
+        <v>75428</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4721,40 +4459,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1204</v>
+        <v>6426</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Väst Krokvattnet, Dls</t>
+          <t>Ebberud, Dls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>347570</v>
+        <v>347197</v>
       </c>
       <c r="R37" t="n">
-        <v>6542693</v>
+        <v>6542713</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4778,17 +4513,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Både äldre och yngre fruktkroppar</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4799,26 +4529,41 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Roger Gran, Anders Niklasson, Leif Appelgren, Roger Adolfsson, Martin Jentzen</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129914801</v>
+        <v>129774295</v>
       </c>
       <c r="B38" t="n">
-        <v>97166</v>
+        <v>75428</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4826,41 +4571,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Väst Krokvattnet, Dls</t>
+          <t>Ebberud, Dls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>347420</v>
+        <v>347491</v>
       </c>
       <c r="R38" t="n">
-        <v>6542738</v>
+        <v>6542667</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4884,17 +4625,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På tallåga i naturskog</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4905,68 +4641,79 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Roger Gran, Anders Niklasson, Leif Appelgren, Roger Adolfsson, Martin Jentzen</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129914872</v>
+        <v>129774301</v>
       </c>
       <c r="B39" t="n">
-        <v>97541</v>
+        <v>75428</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2569</v>
+        <v>6426</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Nordost Rudetjärnet, Dls</t>
+          <t>Ebberud, Dls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>347259</v>
+        <v>347363</v>
       </c>
       <c r="R39" t="n">
-        <v>6542739</v>
+        <v>6542755</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4990,12 +4737,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5006,26 +4753,41 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Roger Gran, Anders Niklasson, Leif Appelgren, Roger Adolfsson, Martin Jentzen</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129914793</v>
+        <v>129774302</v>
       </c>
       <c r="B40" t="n">
-        <v>93048</v>
+        <v>75428</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5033,48 +4795,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5966</v>
+        <v>6426</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Väst Krokvattnet, Dls</t>
+          <t>Ebberud, Dls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>347445</v>
+        <v>347301</v>
       </c>
       <c r="R40" t="n">
-        <v>6542787</v>
+        <v>6542777</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5098,12 +4849,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5114,67 +4865,79 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Roger Gran, Anders Niklasson, Leif Appelgren, Roger Adolfsson, Martin Jentzen</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129914838</v>
+        <v>129774306</v>
       </c>
       <c r="B41" t="n">
-        <v>91501</v>
+        <v>75428</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3215</v>
+        <v>6426</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Nordost Rudetjärnet, Dls</t>
+          <t>Ebberud, Dls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>347253</v>
+        <v>347301</v>
       </c>
       <c r="R41" t="n">
-        <v>6542712</v>
+        <v>6542822</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5198,12 +4961,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5214,73 +4977,79 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Roger Gran, Anders Niklasson, Leif Appelgren, Roger Adolfsson, Martin Jentzen</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129914767</v>
+        <v>129774313</v>
       </c>
       <c r="B42" t="n">
-        <v>4773</v>
+        <v>75428</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100299</v>
+        <v>6426</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Väst Krokvattnet, Dls</t>
+          <t>Ebberud, Dls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>347570</v>
+        <v>347308</v>
       </c>
       <c r="R42" t="n">
-        <v>6542693</v>
+        <v>6542855</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5304,12 +5073,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5320,26 +5089,41 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Roger Gran, Anders Niklasson, Leif Appelgren, Roger Adolfsson, Martin Jentzen</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133641584</v>
+        <v>129774314</v>
       </c>
       <c r="B43" t="n">
-        <v>79985</v>
+        <v>75428</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5347,37 +5131,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>6426</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Krokvattnet, Dls</t>
+          <t>Ebberud, Dls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>347527</v>
+        <v>347318</v>
       </c>
       <c r="R43" t="n">
-        <v>6542759</v>
+        <v>6542859</v>
       </c>
       <c r="S43" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5401,22 +5185,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>15:10</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>15:10</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5427,72 +5201,79 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133641583</v>
+        <v>129774317</v>
       </c>
       <c r="B44" t="n">
-        <v>57162</v>
+        <v>75428</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>6426</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Krokvattnet, Dls</t>
+          <t>Ebberud, Dls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>347526</v>
+        <v>347338</v>
       </c>
       <c r="R44" t="n">
-        <v>6542750</v>
+        <v>6542853</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5516,22 +5297,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>15:09</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>15:09</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5542,72 +5313,79 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133641594</v>
+        <v>129774319</v>
       </c>
       <c r="B45" t="n">
-        <v>57162</v>
+        <v>75428</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100138</v>
+        <v>6426</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Krokvattnet, Dls</t>
+          <t>Ebberud, Dls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>347384</v>
+        <v>347357</v>
       </c>
       <c r="R45" t="n">
-        <v>6542740</v>
+        <v>6542883</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5631,22 +5409,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>16:42</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>16:42</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5657,64 +5425,79 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133641605</v>
+        <v>129774343</v>
       </c>
       <c r="B46" t="n">
-        <v>97803</v>
+        <v>75428</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2569</v>
+        <v>6426</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Krokvattnet, Dls</t>
+          <t>Ebberud, Dls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>347321</v>
+        <v>347452</v>
       </c>
       <c r="R46" t="n">
-        <v>6542863</v>
+        <v>6542896</v>
       </c>
       <c r="S46" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5738,22 +5521,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>17:51</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>17:51</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5764,73 +5537,79 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133641595</v>
+        <v>129774345</v>
       </c>
       <c r="B47" t="n">
-        <v>4776</v>
+        <v>75428</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100299</v>
+        <v>6426</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Krokvattnet, Dls</t>
+          <t>Ebberud, Dls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>347290</v>
+        <v>347402</v>
       </c>
       <c r="R47" t="n">
-        <v>6542793</v>
+        <v>6542883</v>
       </c>
       <c r="S47" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5854,22 +5633,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>16:53</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>16:53</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5880,48 +5649,63 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133641586</v>
+        <v>133641590</v>
       </c>
       <c r="B48" t="n">
-        <v>91930</v>
+        <v>75468</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5931,13 +5715,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>347538</v>
+        <v>347411</v>
       </c>
       <c r="R48" t="n">
-        <v>6542688</v>
+        <v>6542667</v>
       </c>
       <c r="S48" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5966,7 +5750,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5976,7 +5760,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6003,10 +5787,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133641592</v>
+        <v>133641601</v>
       </c>
       <c r="B49" t="n">
-        <v>97428</v>
+        <v>75468</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6014,21 +5798,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6038,13 +5822,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>347424</v>
+        <v>347194</v>
       </c>
       <c r="R49" t="n">
-        <v>6542742</v>
+        <v>6542724</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6073,7 +5857,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6083,7 +5867,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6110,57 +5894,51 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133641585</v>
+        <v>129914900</v>
       </c>
       <c r="B50" t="n">
-        <v>5366</v>
+        <v>75300</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>101728</v>
+        <v>6428</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Krokvattnet, Dls</t>
+          <t>Norr Rudetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>347542</v>
+        <v>347195</v>
       </c>
       <c r="R50" t="n">
-        <v>6542732</v>
+        <v>6542721</v>
       </c>
       <c r="S50" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6184,22 +5962,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>15:14</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>15:14</t>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På klibbal</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6208,51 +5981,50 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Roger Gran, Anders Niklasson, Leif Appelgren, Roger Adolfsson, Martin Jentzen</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133641590</v>
+        <v>133641582</v>
       </c>
       <c r="B51" t="n">
-        <v>75461</v>
+        <v>79992</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6426</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6262,13 +6034,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>347411</v>
+        <v>347474</v>
       </c>
       <c r="R51" t="n">
-        <v>6542667</v>
+        <v>6542831</v>
       </c>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6297,7 +6069,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6307,7 +6079,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6334,32 +6106,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133641591</v>
+        <v>133641584</v>
       </c>
       <c r="B52" t="n">
-        <v>91930</v>
+        <v>79992</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6369,13 +6141,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>347430</v>
+        <v>347527</v>
       </c>
       <c r="R52" t="n">
-        <v>6542734</v>
+        <v>6542759</v>
       </c>
       <c r="S52" t="n">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6404,7 +6176,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6414,7 +6186,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6441,10 +6213,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133641588</v>
+        <v>129568972</v>
       </c>
       <c r="B53" t="n">
-        <v>4776</v>
+        <v>57950</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6452,46 +6224,49 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Krokvattnet, Dls</t>
+          <t>Dyveln, Härserud, Dls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>347481</v>
+        <v>347300</v>
       </c>
       <c r="R53" t="n">
-        <v>6542656</v>
+        <v>6542773</v>
       </c>
       <c r="S53" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6515,22 +6290,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>15:44</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>15:44</t>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Färska rejäla hackspår i en stående död gran. På fyndplatsen finns rikligt med stående död ved av gran.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6541,64 +6311,105 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133641593</v>
+        <v>129569006</v>
       </c>
       <c r="B54" t="n">
-        <v>91967</v>
+        <v>57950</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Krokvattnet, Dls</t>
+          <t>Dyveln, Härserud, Dls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>347390</v>
+        <v>347438</v>
       </c>
       <c r="R54" t="n">
-        <v>6542746</v>
+        <v>6542735</v>
       </c>
       <c r="S54" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6622,22 +6433,17 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>16:35</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>16:35</t>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>En lockande spillkråka i en skog med gott om stående död ved och aspar lämpliga för bohål under kommande häckning.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6648,73 +6454,86 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>Med gran, tall och inslag av asp, björk och rönn.</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133641589</v>
+        <v>129627015</v>
       </c>
       <c r="B55" t="n">
-        <v>5366</v>
+        <v>57950</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>101728</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Krokvattnet, Dls</t>
+          <t>Dyveln, Dls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>347403</v>
+        <v>347315</v>
       </c>
       <c r="R55" t="n">
-        <v>6542690</v>
+        <v>6542796</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6738,22 +6557,27 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Äldre grova hackspår i stambasen av en död tall.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6762,29 +6586,53 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133641604</v>
+        <v>133641583</v>
       </c>
       <c r="B56" t="n">
-        <v>91930</v>
+        <v>57162</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6792,37 +6640,45 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Krokvattnet, Dls</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>347321</v>
+        <v>347526</v>
       </c>
       <c r="R56" t="n">
-        <v>6542863</v>
+        <v>6542750</v>
       </c>
       <c r="S56" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6851,7 +6707,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6861,7 +6717,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6888,10 +6744,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133641587</v>
+        <v>133641594</v>
       </c>
       <c r="B57" t="n">
-        <v>91930</v>
+        <v>57162</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6899,37 +6755,45 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Krokvattnet, Dls</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>347531</v>
+        <v>347384</v>
       </c>
       <c r="R57" t="n">
-        <v>6542681</v>
+        <v>6542740</v>
       </c>
       <c r="S57" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6958,7 +6822,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6968,7 +6832,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6992,6 +6856,1842 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>129774299</v>
+      </c>
+      <c r="B58" t="n">
+        <v>4775</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Ebberud, Dls</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>347399</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6542733</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>129774305</v>
+      </c>
+      <c r="B59" t="n">
+        <v>4775</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Ebberud, Dls</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>347314</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6542809</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>129774312</v>
+      </c>
+      <c r="B60" t="n">
+        <v>4775</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Ebberud, Dls</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>347308</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6542855</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>129774318</v>
+      </c>
+      <c r="B61" t="n">
+        <v>4775</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Ebberud, Dls</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>347344</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6542868</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>129914767</v>
+      </c>
+      <c r="B62" t="n">
+        <v>4775</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Väst Krokvattnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>347570</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6542693</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Roger Gran, Anders Niklasson, Leif Appelgren, Roger Adolfsson, Martin Jentzen</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>133641588</v>
+      </c>
+      <c r="B63" t="n">
+        <v>4776</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Krokvattnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>347481</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6542656</v>
+      </c>
+      <c r="S63" t="n">
+        <v>13</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Joel Nilsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Joel Nilsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>133641595</v>
+      </c>
+      <c r="B64" t="n">
+        <v>4776</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Krokvattnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>347290</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6542793</v>
+      </c>
+      <c r="S64" t="n">
+        <v>19</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Joel Nilsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Joel Nilsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>133641596</v>
+      </c>
+      <c r="B65" t="n">
+        <v>4776</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Krokvattnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>347270</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6542872</v>
+      </c>
+      <c r="S65" t="n">
+        <v>20</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Joel Nilsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Joel Nilsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>129568991</v>
+      </c>
+      <c r="B66" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Dyveln, Härserud, Dls</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>347354</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6542779</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>129774304</v>
+      </c>
+      <c r="B67" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Ebberud, Dls</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>347317</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6542803</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>129774346</v>
+      </c>
+      <c r="B68" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Ebberud, Dls</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>347388</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6542868</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>129774350</v>
+      </c>
+      <c r="B69" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Ebberud, Dls</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>347378</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6542728</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>129556174</v>
+      </c>
+      <c r="B70" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Dyveln, Dyveln, Dls</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>347257</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6542720</v>
+      </c>
+      <c r="S70" t="n">
+        <v>8</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>129569041</v>
+      </c>
+      <c r="B71" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Dyveln, Härserud, Dls</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>347267</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6542704</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>129626512</v>
+      </c>
+      <c r="B72" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Dyveln, Dls</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>347285</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6542754</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>129774351</v>
+      </c>
+      <c r="B73" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Ebberud, Dls</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>347223</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6542771</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY73"/>
+  <dimension ref="A1:AZ73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129774303</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129774316</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129774347</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129774349</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1196,6 +1221,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129914801</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1303,6 +1333,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133641592</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1415,6 +1450,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129774300</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1522,6 +1562,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133641593</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1634,6 +1679,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129774315</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1739,6 +1789,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129914761</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1845,6 +1900,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129914822</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1952,6 +2012,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133641598</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2053,6 +2118,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129914872</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2160,6 +2230,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133641605</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2266,6 +2341,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129914902</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2373,6 +2453,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133641600</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2480,6 +2565,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133641602</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2577,6 +2667,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129774294</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2683,6 +2778,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129914896</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2783,6 +2883,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129914838</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2895,6 +3000,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129774293</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3008,6 +3118,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129774307</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3121,6 +3236,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129774344</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3221,6 +3341,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129914742</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3333,6 +3458,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129774296</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3445,6 +3575,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129774298</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3557,6 +3692,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129774308</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3669,6 +3809,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129774311</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3776,6 +3921,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133641586</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3883,6 +4033,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133641587</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3990,6 +4145,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133641591</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4097,6 +4257,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133641604</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4205,6 +4370,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129914793</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4304,6 +4474,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55840945</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4445,6 +4620,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129626741</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4557,6 +4737,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129774292</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4669,6 +4854,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129774295</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4781,6 +4971,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129774301</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4893,6 +5088,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129774302</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5005,6 +5205,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129774306</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5117,6 +5322,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129774313</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5229,6 +5439,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129774314</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5341,6 +5556,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129774317</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5453,6 +5673,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129774319</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5565,6 +5790,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129774343</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5677,6 +5907,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129774345</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5784,6 +6019,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133641590</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5891,6 +6131,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133641601</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5996,6 +6241,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129914900</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6103,6 +6353,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133641582</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6210,6 +6465,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133641584</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6349,6 +6609,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129568972</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6477,6 +6742,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129569006</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6626,6 +6896,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627015</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6741,6 +7016,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133641583</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6856,6 +7136,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133641594</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6968,6 +7253,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129774299</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7085,6 +7375,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129774305</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7202,6 +7497,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129774312</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7319,6 +7619,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129774318</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7425,6 +7730,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129914767</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7541,6 +7851,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133641588</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7657,6 +7972,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133641595</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7773,6 +8093,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133641596</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7891,6 +8216,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129568991</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8008,6 +8338,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129774304</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8125,6 +8460,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129774346</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8242,6 +8582,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129774350</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8359,6 +8704,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129556174</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8470,6 +8820,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129569041</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8595,6 +8950,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129626512</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8692,8 +9052,87 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129774351</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>